--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-02-2026.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£22.06</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£25.47</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£33.38</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.99</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£42.35</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£779.88</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1019.88</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£28.55</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£32.69</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£42.55</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£40.82</t>
+          <t>£40.99</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£48.17</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>£52.50</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/celotex-cavity-wall-insulation-board-cw4075-1-2m-x-450mm-x-75mm-4-32m2-pack.html (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001D5A07A43D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.58</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1,016.40</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£47.08</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1267.2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradeinsulations.co.uk/product/140mm-celotex-thermaclass/</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
